--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>108.2996059401012</v>
+        <v>17.59868596526644</v>
       </c>
       <c r="D2" t="n">
-        <v>82.94422118002248</v>
+        <v>13.47843594175365</v>
       </c>
       <c r="E2" t="n">
-        <v>32.95335611365404</v>
+        <v>5.354920368468782</v>
       </c>
       <c r="F2" t="n">
-        <v>24.31214368497156</v>
+        <v>3.950723348807879</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.27993385806881</v>
+        <v>3.945489251936181</v>
       </c>
       <c r="D3" t="n">
-        <v>24.20915442044732</v>
+        <v>3.93398759332269</v>
       </c>
       <c r="E3" t="n">
-        <v>32.95335611365404</v>
+        <v>5.354920368468782</v>
       </c>
       <c r="F3" t="n">
-        <v>24.31214368497156</v>
+        <v>3.950723348807879</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.2189197077136</v>
+        <v>10.27307445250346</v>
       </c>
       <c r="D4" t="n">
-        <v>62.37599816436106</v>
+        <v>10.13609970170867</v>
       </c>
       <c r="E4" t="n">
-        <v>32.95335611365404</v>
+        <v>5.354920368468782</v>
       </c>
       <c r="F4" t="n">
-        <v>24.31214368497156</v>
+        <v>3.950723348807879</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>88.53291888963659</v>
+        <v>14.38659931956595</v>
       </c>
       <c r="D5" t="n">
-        <v>65.11693755476868</v>
+        <v>10.58150235264991</v>
       </c>
       <c r="E5" t="n">
-        <v>32.95335611365404</v>
+        <v>5.354920368468782</v>
       </c>
       <c r="F5" t="n">
-        <v>24.31214368497156</v>
+        <v>3.950723348807879</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.36447353880891</v>
+        <v>2.334226950056448</v>
       </c>
       <c r="D6" t="n">
-        <v>13.1909553450216</v>
+        <v>2.143530243566011</v>
       </c>
       <c r="E6" t="n">
-        <v>32.95335611365404</v>
+        <v>5.354920368468782</v>
       </c>
       <c r="F6" t="n">
-        <v>24.31214368497156</v>
+        <v>3.950723348807879</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.88198368407794</v>
+        <v>9.730822348662665</v>
       </c>
       <c r="D7" t="n">
-        <v>58.07639979441252</v>
+        <v>9.437414966592033</v>
       </c>
       <c r="E7" t="n">
-        <v>32.95335611365404</v>
+        <v>5.354920368468782</v>
       </c>
       <c r="F7" t="n">
-        <v>24.31214368497156</v>
+        <v>3.950723348807879</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
